--- a/output/pdf_financials_xlsx/GRID.xlsx
+++ b/output/pdf_financials_xlsx/GRID.xlsx
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0105</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>0</v>
@@ -11795,7 +11795,11 @@
           <t>Share based payment reserve (note 5)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E152" s="5" t="n">
         <v>0.0105</v>
       </c>
@@ -12187,7 +12191,11 @@
           <t>Share based payment reserve (note 4)</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
         <v>0.0105</v>
       </c>

--- a/output/pdf_financials_xlsx/GRID.xlsx
+++ b/output/pdf_financials_xlsx/GRID.xlsx
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.007178</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
     </row>
     <row r="13">
@@ -1180,7 +1180,7 @@
         <v>-0.109764</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.1021</v>
+        <v>-0.09492200000000001</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-6979.436</v>
@@ -1195,7 +1195,7 @@
         <v>-2.616</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.88</v>
+        <v>-0.975</v>
       </c>
     </row>
     <row r="28">
@@ -1236,7 +1236,7 @@
         <v>-0.109764</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.1021</v>
+        <v>-0.09492200000000001</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-5433.699</v>
@@ -1251,7 +1251,7 @@
         <v>-0.864</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.79</v>
+        <v>0.695</v>
       </c>
     </row>
     <row r="30">
@@ -1283,7 +1283,7 @@
         <v>-1.949854437949945</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>1.459907970358324</v>
+        <v>1.284349416960804</v>
       </c>
     </row>
     <row r="31">
@@ -1366,19 +1366,19 @@
         <v>0.516134</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>14203.794</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>5850.914</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.153698</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>13.219</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>12.618</v>
       </c>
     </row>
     <row r="35">
@@ -1422,19 +1422,19 @@
         <v>0.516134</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>14203.794</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>5850.914</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.153698</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>13.219</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>12.618</v>
       </c>
     </row>
     <row r="37">
@@ -1758,19 +1758,19 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5985.795</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>8288.977999999999</v>
+        <v>2438.064</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>7.293029</v>
+        <v>2.139331</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>15.048</v>
+        <v>1.829</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>14.622</v>
+        <v>2.004</v>
       </c>
     </row>
     <row r="49">
@@ -3921,13 +3921,13 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-2.262857</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-4.821</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="125">
@@ -3949,13 +3949,13 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-2.262857</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-4.821</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-4.245</v>
       </c>
     </row>
     <row r="126">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -13238,7 +13238,11 @@
           <t>Repayment of indebtedness</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -14554,7 +14558,11 @@
           <t>Repayments of indebtedness 12</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -18100,7 +18108,7 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -22467,7 +22475,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRID.xlsx
+++ b/output/pdf_financials_xlsx/GRID.xlsx
@@ -3243,19 +3243,19 @@
         <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>596.804</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>865.35</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.7699009999999999</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="101">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRID.xlsx
+++ b/output/pdf_financials_xlsx/GRID.xlsx
@@ -2318,13 +2318,13 @@
         <v>0</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>5.250974</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>6.187</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>5.728</v>
       </c>
     </row>
     <row r="68">
@@ -2396,19 +2396,19 @@
         <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>726.549</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>858.643</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.857273</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.843</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="71">
@@ -2424,19 +2424,19 @@
         <v>0</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>726.549</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>858.643</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.857273</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.843</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.746</v>
       </c>
     </row>
     <row r="72">
@@ -2542,13 +2542,13 @@
         <v>0</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>13.541135</v>
+        <v>12.683862</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>12.111</v>
+        <v>11.268</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>10.551</v>
+        <v>9.805</v>
       </c>
     </row>
     <row r="76">
@@ -2683,30 +2683,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>0.1069932964716094</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.239931606430158</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.3697178876984822</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.1214522403111944</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.09944014929352173</v>
       </c>
     </row>
     <row r="81">
@@ -3265,10 +3255,10 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005248</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.005248</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>3552.599</v>
@@ -3405,10 +3395,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.064238</v>
+        <v>0.05899</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.024356</v>
+        <v>-0.019108</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-962.908</v>
@@ -3551,19 +3541,19 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-147.59</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-176.548</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.269361</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.409</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.753</v>
       </c>
     </row>
     <row r="112">
@@ -3691,7 +3681,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-382.621</v>
       </c>
       <c r="E116" s="3" t="n">
         <v>0</v>
@@ -4209,19 +4199,19 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-147.59</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-176.548</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.269361</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.409</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.753</v>
       </c>
     </row>
     <row r="135">
@@ -4237,19 +4227,19 @@
         <v>-0.110401</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-4014.211</v>
+        <v>-4161.801</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-3399.032</v>
+        <v>-3575.58</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-0.839724</v>
+        <v>-1.109085</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>2.638</v>
+        <v>2.229</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>4.715</v>
+        <v>3.962</v>
       </c>
     </row>
   </sheetData>
@@ -4945,7 +4935,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -5196,7 +5190,11 @@
           <t>Lease liabilities</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -5865,7 +5863,11 @@
           <t>Lease liabilities 13</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -10869,7 +10871,11 @@
           <t>Lease liabilities 14</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
@@ -13142,7 +13148,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -14509,7 +14519,11 @@
           <t>Purchase of equipment 8</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -15656,7 +15670,11 @@
           <t>Purchase of equipment 9</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr"/>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -15703,7 +15721,11 @@
           <t>Purchase of intangible assets 10</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -16760,7 +16782,11 @@
           <t>GST recoverable</t>
         </is>
       </c>
-      <c r="D251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E251" s="5" t="n">
         <v>-0.005248</v>
       </c>
@@ -22073,7 +22099,11 @@
           <t>Income tax (recovery) expense 17</t>
         </is>
       </c>
-      <c r="D356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E356" t="inlineStr">
         <is>
           <t>-</t>
